--- a/samples/Drone_ROI_Output_sample.xlsx
+++ b/samples/Drone_ROI_Output_sample.xlsx
@@ -80,7 +80,7 @@
     <t>Europe</t>
   </si>
   <si>
-    <t>Baseline — matches the published acceptance figures</t>
+    <t>Baseline, matches the published acceptance figures</t>
   </si>
   <si>
     <t>calculated</t>
@@ -140,7 +140,7 @@
     <t>Wind Farm</t>
   </si>
   <si>
-    <t>Renewable assets — target scaling is fractional (168.75)</t>
+    <t>Renewable assets, target scaling is fractional (168.75)</t>
   </si>
   <si>
     <t>Tata Steel</t>
@@ -197,7 +197,7 @@
     <t>Met Mast Alpha</t>
   </si>
   <si>
-    <t>Negative saving at current area — labour case does not stand alone</t>
+    <t>Negative saving at current area, labour case does not stand alone</t>
   </si>
   <si>
     <t>tier improves at target</t>
@@ -281,7 +281,7 @@
     <t>current</t>
   </si>
   <si>
-    <t>TARGET AREA — resources scaled linearly, operator ratio switched to at-scale</t>
+    <t>TARGET AREA, resources scaled linearly, operator ratio switched to at-scale</t>
   </si>
   <si>
     <t>Target area</t>
@@ -323,7 +323,7 @@
     <t>target area ÷ current area (1.0 at the current area by definition)</t>
   </si>
   <si>
-    <t>1.0 by definition — this is the present state</t>
+    <t>1.0 by definition, this is the present state</t>
   </si>
   <si>
     <t>120,000 ÷ 60,000 = 2</t>
@@ -335,7 +335,7 @@
     <t>100 as supplied by the customer</t>
   </si>
   <si>
-    <t>100 × 2 = 200 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>100 × 2 = 200 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>Manual hours per year</t>
@@ -395,7 +395,7 @@
     <t>Docks required</t>
   </si>
   <si>
-    <t>docks before rounding, rounded up — a dock is a purchase, so part of one is a whole one</t>
+    <t>docks before rounding, rounded up, a dock is a purchase, so part of one is a whole one</t>
   </si>
   <si>
     <t>round up 27.4 = 28</t>
@@ -419,7 +419,7 @@
     <t>Operators required</t>
   </si>
   <si>
-    <t>operators before rounding, rounded up — an operator is a hire</t>
+    <t>operators before rounding, rounded up, an operator is a hire</t>
   </si>
   <si>
     <t>round up 7 = 7</t>
@@ -491,7 +491,7 @@
     <t>Manual cost per sq ft</t>
   </si>
   <si>
-    <t>manual cost ÷ area priced — a display metric, not a driver of the model</t>
+    <t>manual cost ÷ area priced, a display metric, not a driver of the model</t>
   </si>
   <si>
     <t>8,000,000 ÷ 60,000 = 133.33</t>
@@ -503,7 +503,7 @@
     <t>Autonomous cost per sq ft</t>
   </si>
   <si>
-    <t>autonomous cost ÷ area priced — a display metric, not a driver of the model</t>
+    <t>autonomous cost ÷ area priced, a display metric, not a driver of the model</t>
   </si>
   <si>
     <t>1,820,000 ÷ 60,000 = 30.33</t>
@@ -515,7 +515,7 @@
     <t>Annual saving per sq ft</t>
   </si>
   <si>
-    <t>annual saving ÷ area priced — a display metric, not a driver of the model</t>
+    <t>annual saving ÷ area priced, a display metric, not a driver of the model</t>
   </si>
   <si>
     <t>6,180,000 ÷ 60,000 = 103</t>
@@ -524,7 +524,7 @@
     <t>12,725,000 ÷ 120,000 = 106.04</t>
   </si>
   <si>
-    <t>— parameter sources —</t>
+    <t xml:space="preserve">, parameter sources, </t>
   </si>
   <si>
     <t>dockHours</t>
@@ -599,7 +599,7 @@
     <t>140 as supplied by the customer</t>
   </si>
   <si>
-    <t>140 × 2 = 280 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>140 × 2 = 280 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>140 × 8 × 300 = 336,000</t>
@@ -701,7 +701,7 @@
     <t>180 as supplied by the customer</t>
   </si>
   <si>
-    <t>180 × 2 = 360 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>180 × 2 = 360 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>180 × 10 × 320 = 576,000</t>
@@ -803,7 +803,7 @@
     <t>60 as supplied by the customer</t>
   </si>
   <si>
-    <t>60 × 2 = 120 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>60 × 2 = 120 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>60 × 8 × 300 = 144,000</t>
@@ -905,7 +905,7 @@
     <t>320 as supplied by the customer</t>
   </si>
   <si>
-    <t>320 × 2.0455 = 654.55 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>320 × 2.0455 = 654.55 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>320 × 12 × 330 = 1,267,200</t>
@@ -1010,7 +1010,7 @@
     <t>90 as supplied by the customer</t>
   </si>
   <si>
-    <t>90 × 1.875 = 168.75 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>90 × 1.875 = 168.75 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>90 × 8 × 310 = 223,200</t>
@@ -1115,7 +1115,7 @@
     <t>85 as supplied by the customer</t>
   </si>
   <si>
-    <t>85 × 2 = 170 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>85 × 2 = 170 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>85 × 8 × 300 = 204,000</t>
@@ -1214,7 +1214,7 @@
     <t>260 as supplied by the customer</t>
   </si>
   <si>
-    <t>260 × 1.9444 = 505.56 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>260 × 1.9444 = 505.56 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>260 × 12 × 330 = 1,029,600</t>
@@ -1313,7 +1313,7 @@
     <t>130 as supplied by the customer</t>
   </si>
   <si>
-    <t>130 × 1.8947 = 246.32 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>130 × 1.8947 = 246.32 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>130 × 8 × 300 = 312,000</t>
@@ -1418,7 +1418,7 @@
     <t>220 as supplied by the customer</t>
   </si>
   <si>
-    <t>220 × 2 = 440 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>220 × 2 = 440 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>220 × 10 × 320 = 704,000</t>
@@ -1520,7 +1520,7 @@
     <t>2 as supplied by the customer</t>
   </si>
   <si>
-    <t>2 × 1.5 = 3 (kept fractional — an extrapolation of the customer's headcount, not a purchase)</t>
+    <t>2 × 1.5 = 3 (kept fractional, an extrapolation of the customer's headcount, not a purchase)</t>
   </si>
   <si>
     <t>2 × 8 × 260 = 4,160</t>
@@ -1583,7 +1583,7 @@
     <t>10,000 ÷ 125,000 = 0.08</t>
   </si>
   <si>
-    <t>no payback at these inputs — the model does not save money here</t>
+    <t>no payback at these inputs, the model does not save money here</t>
   </si>
   <si>
     <t>250,000 ÷ (10,000 ÷ 12) = 300</t>
@@ -1622,7 +1622,7 @@
     <t>Every series below is bound to a cell range on the Executive Summary sheet.</t>
   </si>
   <si>
-    <t>Edit a figure there and these charts move with it — they are not pictures.</t>
+    <t>Edit a figure there and these charts move with it, they are not pictures.</t>
   </si>
   <si>
     <t>Kind</t>
@@ -1640,7 +1640,7 @@
     <t>salary</t>
   </si>
   <si>
-    <t>AUTONOMOUS INSPECTION ROI — MODEL OUTPUT</t>
+    <t>AUTONOMOUS INSPECTION ROI, MODEL OUTPUT</t>
   </si>
   <si>
     <t>Generated by the Drone ROI engine. Every figure derives from the model below.</t>
@@ -1649,25 +1649,25 @@
     <t>WHAT EACH SHEET CONTAINS</t>
   </si>
   <si>
-    <t>Executive Summary — one row per site. Original input columns first, in their original order, then the calculated columns. Rows that could not be priced show blank figures and a status of "model incomplete".</t>
-  </si>
-  <si>
-    <t>Detailed Calculations — every intermediate value, for the current area and again for the target area. The target block is separated by a header band.</t>
-  </si>
-  <si>
-    <t>Audit Trail — each formula in plain English with its inputs and computed value, per site, plus the resolved source of every autonomous parameter.</t>
-  </si>
-  <si>
-    <t>Sensitivity Analysis — autonomous cost and cost ratio at docks-per-operator of 2, 4, 6 and 8, per site, at the current area.</t>
-  </si>
-  <si>
-    <t>Charts — native Excel charts bound to cell ranges on the Executive Summary. Editing a figure there moves the chart. These are not images.</t>
-  </si>
-  <si>
-    <t>Exceptions — invalid or skipped rows with a specific reason each. Omitted when empty.</t>
-  </si>
-  <si>
-    <t>Original Input — the source worksheet, unmodified.</t>
+    <t>Executive Summary, one row per site. Original input columns first, in their original order, then the calculated columns. Rows that could not be priced show blank figures and a status of "model incomplete".</t>
+  </si>
+  <si>
+    <t>Detailed Calculations, every intermediate value, for the current area and again for the target area. The target block is separated by a header band.</t>
+  </si>
+  <si>
+    <t>Audit Trail, each formula in plain English with its inputs and computed value, per site, plus the resolved source of every autonomous parameter.</t>
+  </si>
+  <si>
+    <t>Sensitivity Analysis, autonomous cost and cost ratio at docks-per-operator of 2, 4, 6 and 8, per site, at the current area.</t>
+  </si>
+  <si>
+    <t>Charts, native Excel charts bound to cell ranges on the Executive Summary. Editing a figure there moves the chart. These are not images.</t>
+  </si>
+  <si>
+    <t>Exceptions, invalid or skipped rows with a specific reason each. Omitted when empty.</t>
+  </si>
+  <si>
+    <t>Original Input, the source worksheet, unmodified.</t>
   </si>
   <si>
     <t>THE MODEL</t>
@@ -1715,7 +1715,7 @@
     <t>Docks and operators each round up, independently. A dock is a purchase and an operator is a hire: you cannot buy four tenths of a dock or hire a fifth of a person. The operator ratio is applied to the whole dock count, never to a fractional one.</t>
   </si>
   <si>
-    <t>Manual resources at the target area are NOT rounded. They are a linear extrapolation of the customer's own staffing that nobody has committed to, not something we procure — a different epistemic status, so a different rule. Rounding 168.75 up to 169 would also inflate manual cost, which flatters the seller, and would turn manual cost into a step function that obscures the linear-versus-sub-linear contrast the target scenario exists to show. Target-area resources are therefore shown to two decimal places.</t>
+    <t>Manual resources at the target area are NOT rounded. They are a linear extrapolation of the customer's own staffing that nobody has committed to, not something we procure, a different epistemic status, so a different rule. Rounding 168.75 up to 169 would also inflate manual cost, which flatters the seller, and would turn manual cost into a step function that obscures the linear-versus-sub-linear contrast the target scenario exists to show. Target-area resources are therefore shown to two decimal places.</t>
   </si>
   <si>
     <t>THE TARGET-AREA SCENARIO</t>
@@ -1730,7 +1730,7 @@
     <t>Area enters the model only as the ratio targetArea / area, and as the denominator of the cost-per-unit-area display lines. The model does not price per square foot. If a customer engineer asks where the square footage went, that is the honest answer.</t>
   </si>
   <si>
-    <t>An optional Area Unit column is read if present. If the current and target areas carry different units, the row is not priced and appears in Exceptions. If no unit is given, both areas are assumed to share whatever unit the customer used — safe exactly as long as they match. A scale factor outside roughly 0.1x to 50x raises a warning, because that band catches a square-feet-against-acres mix-up without refusing a genuine tenfold expansion.</t>
+    <t>An optional Area Unit column is read if present. If the current and target areas carry different units, the row is not priced and appears in Exceptions. If no unit is given, both areas are assumed to share whatever unit the customer used, safe exactly as long as they match. A scale factor outside roughly 0.1x to 50x raises a warning, because that band catches a square-feet-against-acres mix-up without refusing a genuine tenfold expansion.</t>
   </si>
   <si>
     <t>ROW VALIDATION</t>
@@ -1763,7 +1763,7 @@
     <t>4. otherwise                                  -&gt;  "Marginal on labour alone, requires additional value pools to justify"</t>
   </si>
   <si>
-    <t>Both conditions are required in tiers 1 and 2 — not either. Invalid rows receive no recommendation at all.</t>
+    <t>Both conditions are required in tiers 1 and 2, not either. Invalid rows receive no recommendation at all.</t>
   </si>
   <si>
     <t>Where the current and target areas fall into different tiers, the Status column says so ("tier improves at target" or "tier weakens at target"). That is a signal, not a conflict, and neither figure is silently preferred.</t>
@@ -1775,7 +1775,7 @@
     <t>PARAMETER RESOLUTION</t>
   </si>
   <si>
-    <t>Each autonomous parameter is resolved in this order: a per-row override column, then a Parameters sheet in the input workbook, then the built-in default. The source is recorded for every parameter of every site in the Audit Trail. A tier that supplies a present-but-invalid value does not fall through silently — the rejection is recorded.</t>
+    <t>Each autonomous parameter is resolved in this order: a per-row override column, then a Parameters sheet in the input workbook, then the built-in default. The source is recorded for every parameter of every site in the Audit Trail. A tier that supplies a present-but-invalid value does not fall through silently, the rejection is recorded.</t>
   </si>
   <si>
     <t>SOURCE OF EVERY DEFAULT</t>
